--- a/Result/profitability/6221.xlsx
+++ b/Result/profitability/6221.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6712499999999999</v>
+        <v>0.66125</v>
       </c>
       <c r="N2" t="n">
-        <v>20.61625</v>
+        <v>22.0425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.57625</v>
+        <v>0.5475</v>
       </c>
       <c r="N3" t="n">
-        <v>19.97125</v>
+        <v>21.72125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4775</v>
+        <v>0.48875</v>
       </c>
       <c r="N4" t="n">
-        <v>19.47375</v>
+        <v>21.4975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.39375</v>
+        <v>0.395</v>
       </c>
       <c r="N5" t="n">
-        <v>19.9625</v>
+        <v>21.59</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.285</v>
+        <v>0.31625</v>
       </c>
       <c r="N6" t="n">
-        <v>19.58125</v>
+        <v>21.5825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1575</v>
+        <v>0.2025</v>
       </c>
       <c r="N7" t="n">
-        <v>20.28125</v>
+        <v>22.03375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05499999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="N8" t="n">
-        <v>19.65375</v>
+        <v>21.70125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6221</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>941</v>
+      </c>
+      <c r="D75" t="n">
+        <v>610</v>
+      </c>
+      <c r="E75" t="n">
+        <v>332</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>173</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>200</v>
+      </c>
+      <c r="K75" t="n">
+        <v>146</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.60125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.485714285714286</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.868965517241379</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.01162790697674421</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5862224223322825</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
